--- a/AccelerationDueToRod.xlsx
+++ b/AccelerationDueToRod.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hypehuman\Ahmil\My Code\Mechanics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86D02D47-0127-42AA-BC20-03C2814C56DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E72D7BF-0D0E-4C89-8AB2-90A978F145BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{BCCF6670-327D-4911-AE2C-89989FE77C33}"/>
+    <workbookView xWindow="38550" yWindow="5730" windowWidth="26445" windowHeight="14130" xr2:uid="{BCCF6670-327D-4911-AE2C-89989FE77C33}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -129,8 +129,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -234,21 +235,6 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="poly"/>
-            <c:order val="6"/>
-            <c:dispRSqr val="0"/>
-            <c:dispEq val="0"/>
-          </c:trendline>
           <c:xVal>
             <c:numRef>
               <c:f>Sheet1!$K$2:$K$34</c:f>
@@ -304,43 +290,43 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="33"/>
                 <c:pt idx="0">
-                  <c:v>-0.49971559905464596</c:v>
+                  <c:v>3.335251822770423E-11</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-0.76119573368969262</c:v>
+                  <c:v>5.0804486853651148E-11</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-1.3308396281265527</c:v>
+                  <c:v>8.8824229300050502E-11</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-3.1797681697447895</c:v>
+                  <c:v>2.1222726695327648E-10</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-77.957160285867374</c:v>
+                  <c:v>5.2030947489596425E-9</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-2.6470380549989185</c:v>
+                  <c:v>1.7667126090479272E-10</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-1.3322676295501878E-15</c:v>
+                  <c:v>-3.5866034372416434E-25</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.6470380549989088</c:v>
+                  <c:v>-1.7667126090479192E-10</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>77.95716028586736</c:v>
+                  <c:v>-5.2030947489596449E-9</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3.1797681697447899</c:v>
+                  <c:v>-2.122272669532765E-10</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.3308396281265527</c:v>
+                  <c:v>-8.8824229300050502E-11</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.76119573368969251</c:v>
+                  <c:v>-5.0804486853651142E-11</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.49971559905464585</c:v>
+                  <c:v>-3.335251822770423E-11</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -368,6 +354,7 @@
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="2"/>
+          <c:min val="-1"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
@@ -1102,15 +1089,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>552450</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>90487</xdr:rowOff>
+      <xdr:colOff>133350</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>119062</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>514350</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>166687</xdr:rowOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>4762</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1460,16 +1447,19 @@
   <cols>
     <col min="1" max="1" width="8.28515625" customWidth="1"/>
     <col min="2" max="2" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="2.7109375" customWidth="1"/>
     <col min="5" max="5" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="2.7109375" customWidth="1"/>
     <col min="7" max="7" width="7.42578125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="2.7109375" customWidth="1"/>
     <col min="10" max="11" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1">
-        <v>1</v>
+      <c r="A1" s="1">
+        <v>6.6742999999999994E-11</v>
       </c>
       <c r="B1" t="s">
         <v>5</v>
@@ -1515,7 +1505,7 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <f>$A$3+$D$1*(G2+0.5)/$A$5</f>
+        <f t="shared" ref="H2:H18" si="0">$A$3+$D$1*(G2+0.5)/$A$5</f>
         <v>3.125E-2</v>
       </c>
       <c r="J2">
@@ -1526,8 +1516,8 @@
         <v>-1</v>
       </c>
       <c r="L2" cm="1">
-        <f t="array" ref="L2">SUM(VALUE(IF(ISNUMBER(H:H),$A$1*$A$2*$D$2*SIGN(J2-H:H)/(J2-H:H)^2,0)))</f>
-        <v>-0.49971559905464596</v>
+        <f t="array" ref="L2">SUM(VALUE(IF(ISNUMBER(H:H),$A$1*$A$2*$D$2*SIGN(H:H-J2)/(H:H-J2)^2,0)))</f>
+        <v>3.335251822770423E-11</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -1538,11 +1528,11 @@
         <v>7</v>
       </c>
       <c r="G3">
-        <f>IF(G2+1&lt;$A$5,G2+1,0/0)</f>
+        <f t="shared" ref="G3:G18" si="1">IF(G2+1&lt;$A$5,G2+1,0/0)</f>
         <v>1</v>
       </c>
       <c r="H3">
-        <f>$A$3+$D$1*(G3+0.5)/$A$5</f>
+        <f t="shared" si="0"/>
         <v>9.375E-2</v>
       </c>
       <c r="J3">
@@ -1550,12 +1540,12 @@
         <v>-0.75</v>
       </c>
       <c r="K3">
-        <f t="shared" ref="K3:K14" si="0">J3-$A$3</f>
+        <f t="shared" ref="K3:K14" si="2">J3-$A$3</f>
         <v>-0.75</v>
       </c>
       <c r="L3" cm="1">
-        <f t="array" ref="L3">SUM(VALUE(IF(ISNUMBER(H:H),$A$1*$A$2*$D$2*SIGN(J3-H:H)/(J3-H:H)^2,0)))</f>
-        <v>-0.76119573368969262</v>
+        <f t="array" ref="L3">SUM(VALUE(IF(ISNUMBER(H:H),$A$1*$A$2*$D$2*SIGN(H:H-J3)/(H:H-J3)^2,0)))</f>
+        <v>5.0804486853651148E-11</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -1566,24 +1556,24 @@
         <v>8</v>
       </c>
       <c r="G4">
-        <f>IF(G3+1&lt;$A$5,G3+1,0/0)</f>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="H4">
-        <f>$A$3+$D$1*(G4+0.5)/$A$5</f>
+        <f t="shared" si="0"/>
         <v>0.15625</v>
       </c>
       <c r="J4">
-        <f t="shared" ref="J4:J10" si="1">J3+(1/4)</f>
+        <f t="shared" ref="J4:J10" si="3">J3+(1/4)</f>
         <v>-0.5</v>
       </c>
       <c r="K4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>-0.5</v>
       </c>
       <c r="L4" cm="1">
-        <f t="array" ref="L4">SUM(VALUE(IF(ISNUMBER(H:H),$A$1*$A$2*$D$2*SIGN(J4-H:H)/(J4-H:H)^2,0)))</f>
-        <v>-1.3308396281265527</v>
+        <f t="array" ref="L4">SUM(VALUE(IF(ISNUMBER(H:H),$A$1*$A$2*$D$2*SIGN(H:H-J4)/(H:H-J4)^2,0)))</f>
+        <v>8.8824229300050502E-11</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
@@ -1594,261 +1584,261 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <f>IF(G4+1&lt;$A$5,G4+1,0/0)</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="H5">
-        <f>$A$3+$D$1*(G5+0.5)/$A$5</f>
+        <f t="shared" si="0"/>
         <v>0.21875</v>
       </c>
       <c r="J5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>-0.25</v>
       </c>
       <c r="K5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>-0.25</v>
       </c>
       <c r="L5" cm="1">
-        <f t="array" ref="L5">SUM(VALUE(IF(ISNUMBER(H:H),$A$1*$A$2*$D$2*SIGN(J5-H:H)/(J5-H:H)^2,0)))</f>
-        <v>-3.1797681697447895</v>
+        <f t="array" ref="L5">SUM(VALUE(IF(ISNUMBER(H:H),$A$1*$A$2*$D$2*SIGN(H:H-J5)/(H:H-J5)^2,0)))</f>
+        <v>2.1222726695327648E-10</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="G6">
-        <f>IF(G5+1&lt;$A$5,G5+1,0/0)</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="H6">
-        <f>$A$3+$D$1*(G6+0.5)/$A$5</f>
+        <f t="shared" si="0"/>
         <v>0.28125</v>
       </c>
       <c r="J6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L6" cm="1">
-        <f t="array" ref="L6">SUM(VALUE(IF(ISNUMBER(H:H),$A$1*$A$2*$D$2*SIGN(J6-H:H)/(J6-H:H)^2,0)))</f>
-        <v>-77.957160285867374</v>
+        <f t="array" ref="L6">SUM(VALUE(IF(ISNUMBER(H:H),$A$1*$A$2*$D$2*SIGN(H:H-J6)/(H:H-J6)^2,0)))</f>
+        <v>5.2030947489596425E-9</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="G7">
-        <f>IF(G6+1&lt;$A$5,G6+1,0/0)</f>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="H7">
-        <f>$A$3+$D$1*(G7+0.5)/$A$5</f>
+        <f t="shared" si="0"/>
         <v>0.34375</v>
       </c>
       <c r="J7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.25</v>
       </c>
       <c r="K7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.25</v>
       </c>
       <c r="L7" cm="1">
-        <f t="array" ref="L7">SUM(VALUE(IF(ISNUMBER(H:H),$A$1*$A$2*$D$2*SIGN(J7-H:H)/(J7-H:H)^2,0)))</f>
-        <v>-2.6470380549989185</v>
+        <f t="array" ref="L7">SUM(VALUE(IF(ISNUMBER(H:H),$A$1*$A$2*$D$2*SIGN(H:H-J7)/(H:H-J7)^2,0)))</f>
+        <v>1.7667126090479272E-10</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="G8">
-        <f>IF(G7+1&lt;$A$5,G7+1,0/0)</f>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="H8">
-        <f>$A$3+$D$1*(G8+0.5)/$A$5</f>
+        <f t="shared" si="0"/>
         <v>0.40625</v>
       </c>
       <c r="J8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.5</v>
       </c>
       <c r="K8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
       <c r="L8" cm="1">
-        <f t="array" ref="L8">SUM(VALUE(IF(ISNUMBER(H:H),$A$1*$A$2*$D$2*SIGN(J8-H:H)/(J8-H:H)^2,0)))</f>
-        <v>-1.3322676295501878E-15</v>
+        <f t="array" ref="L8">SUM(VALUE(IF(ISNUMBER(H:H),$A$1*$A$2*$D$2*SIGN(H:H-J8)/(H:H-J8)^2,0)))</f>
+        <v>-3.5866034372416434E-25</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="G9">
-        <f>IF(G8+1&lt;$A$5,G8+1,0/0)</f>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="H9">
-        <f>$A$3+$D$1*(G9+0.5)/$A$5</f>
+        <f t="shared" si="0"/>
         <v>0.46875</v>
       </c>
       <c r="J9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.75</v>
       </c>
       <c r="K9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.75</v>
       </c>
       <c r="L9" cm="1">
-        <f t="array" ref="L9">SUM(VALUE(IF(ISNUMBER(H:H),$A$1*$A$2*$D$2*SIGN(J9-H:H)/(J9-H:H)^2,0)))</f>
-        <v>2.6470380549989088</v>
+        <f t="array" ref="L9">SUM(VALUE(IF(ISNUMBER(H:H),$A$1*$A$2*$D$2*SIGN(H:H-J9)/(H:H-J9)^2,0)))</f>
+        <v>-1.7667126090479192E-10</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="G10">
-        <f>IF(G9+1&lt;$A$5,G9+1,0/0)</f>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="H10">
-        <f>$A$3+$D$1*(G10+0.5)/$A$5</f>
+        <f t="shared" si="0"/>
         <v>0.53125</v>
       </c>
       <c r="J10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="K10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="L10" cm="1">
-        <f t="array" ref="L10">SUM(VALUE(IF(ISNUMBER(H:H),$A$1*$A$2*$D$2*SIGN(J10-H:H)/(J10-H:H)^2,0)))</f>
-        <v>77.95716028586736</v>
+        <f t="array" ref="L10">SUM(VALUE(IF(ISNUMBER(H:H),$A$1*$A$2*$D$2*SIGN(H:H-J10)/(H:H-J10)^2,0)))</f>
+        <v>-5.2030947489596449E-9</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="G11">
-        <f>IF(G10+1&lt;$A$5,G10+1,0/0)</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="H11">
-        <f>$A$3+$D$1*(G11+0.5)/$A$5</f>
+        <f t="shared" si="0"/>
         <v>0.59375</v>
       </c>
       <c r="J11">
-        <f t="shared" ref="J11:J14" si="2">J10+(1/4)</f>
+        <f t="shared" ref="J11:J14" si="4">J10+(1/4)</f>
         <v>1.25</v>
       </c>
       <c r="K11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1.25</v>
       </c>
       <c r="L11" cm="1">
-        <f t="array" ref="L11">SUM(VALUE(IF(ISNUMBER(H:H),$A$1*$A$2*$D$2*SIGN(J11-H:H)/(J11-H:H)^2,0)))</f>
-        <v>3.1797681697447899</v>
+        <f t="array" ref="L11">SUM(VALUE(IF(ISNUMBER(H:H),$A$1*$A$2*$D$2*SIGN(H:H-J11)/(H:H-J11)^2,0)))</f>
+        <v>-2.122272669532765E-10</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="G12">
-        <f>IF(G11+1&lt;$A$5,G11+1,0/0)</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="H12">
-        <f>$A$3+$D$1*(G12+0.5)/$A$5</f>
+        <f t="shared" si="0"/>
         <v>0.65625</v>
       </c>
       <c r="J12">
+        <f t="shared" si="4"/>
+        <v>1.5</v>
+      </c>
+      <c r="K12">
         <f t="shared" si="2"/>
         <v>1.5</v>
       </c>
-      <c r="K12">
-        <f t="shared" si="0"/>
-        <v>1.5</v>
-      </c>
       <c r="L12" cm="1">
-        <f t="array" ref="L12">SUM(VALUE(IF(ISNUMBER(H:H),$A$1*$A$2*$D$2*SIGN(J12-H:H)/(J12-H:H)^2,0)))</f>
-        <v>1.3308396281265527</v>
+        <f t="array" ref="L12">SUM(VALUE(IF(ISNUMBER(H:H),$A$1*$A$2*$D$2*SIGN(H:H-J12)/(H:H-J12)^2,0)))</f>
+        <v>-8.8824229300050502E-11</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="G13">
-        <f>IF(G12+1&lt;$A$5,G12+1,0/0)</f>
+        <f t="shared" si="1"/>
         <v>11</v>
       </c>
       <c r="H13">
-        <f>$A$3+$D$1*(G13+0.5)/$A$5</f>
+        <f t="shared" si="0"/>
         <v>0.71875</v>
       </c>
       <c r="J13">
+        <f t="shared" si="4"/>
+        <v>1.75</v>
+      </c>
+      <c r="K13">
         <f t="shared" si="2"/>
         <v>1.75</v>
       </c>
-      <c r="K13">
-        <f t="shared" si="0"/>
-        <v>1.75</v>
-      </c>
       <c r="L13" cm="1">
-        <f t="array" ref="L13">SUM(VALUE(IF(ISNUMBER(H:H),$A$1*$A$2*$D$2*SIGN(J13-H:H)/(J13-H:H)^2,0)))</f>
-        <v>0.76119573368969251</v>
+        <f t="array" ref="L13">SUM(VALUE(IF(ISNUMBER(H:H),$A$1*$A$2*$D$2*SIGN(H:H-J13)/(H:H-J13)^2,0)))</f>
+        <v>-5.0804486853651142E-11</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="G14">
-        <f>IF(G13+1&lt;$A$5,G13+1,0/0)</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="H14">
-        <f>$A$3+$D$1*(G14+0.5)/$A$5</f>
+        <f t="shared" si="0"/>
         <v>0.78125</v>
       </c>
       <c r="J14">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="K14">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="K14">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
       <c r="L14" cm="1">
-        <f t="array" ref="L14">SUM(VALUE(IF(ISNUMBER(H:H),$A$1*$A$2*$D$2*SIGN(J14-H:H)/(J14-H:H)^2,0)))</f>
-        <v>0.49971559905464585</v>
+        <f t="array" ref="L14">SUM(VALUE(IF(ISNUMBER(H:H),$A$1*$A$2*$D$2*SIGN(H:H-J14)/(H:H-J14)^2,0)))</f>
+        <v>-3.335251822770423E-11</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="G15">
-        <f>IF(G14+1&lt;$A$5,G14+1,0/0)</f>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="H15">
-        <f>$A$3+$D$1*(G15+0.5)/$A$5</f>
+        <f t="shared" si="0"/>
         <v>0.84375</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="G16">
-        <f>IF(G15+1&lt;$A$5,G15+1,0/0)</f>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="H16">
-        <f>$A$3+$D$1*(G16+0.5)/$A$5</f>
+        <f t="shared" si="0"/>
         <v>0.90625</v>
       </c>
     </row>
     <row r="17" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G17">
-        <f>IF(G16+1&lt;$A$5,G16+1,0/0)</f>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
       <c r="H17">
-        <f>$A$3+$D$1*(G17+0.5)/$A$5</f>
+        <f t="shared" si="0"/>
         <v>0.96875</v>
       </c>
     </row>
     <row r="18" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G18" t="e">
-        <f>IF(G17+1&lt;$A$5,G17+1,0/0)</f>
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H18" t="e">
-        <f>$A$3+$D$1*(G18+0.5)/$A$5</f>
+        <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
     </row>

--- a/AccelerationDueToRod.xlsx
+++ b/AccelerationDueToRod.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hypehuman\Ahmil\My Code\Mechanics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E72D7BF-0D0E-4C89-8AB2-90A978F145BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6729257-3623-4D09-8A6A-0BB45C0188A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38550" yWindow="5730" windowWidth="26445" windowHeight="14130" xr2:uid="{BCCF6670-327D-4911-AE2C-89989FE77C33}"/>
+    <workbookView xWindow="4680" yWindow="4680" windowWidth="26445" windowHeight="14130" xr2:uid="{BCCF6670-327D-4911-AE2C-89989FE77C33}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,38 +35,13 @@
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>Number of pieces</t>
   </si>
   <si>
     <t>M</t>
-  </si>
-  <si>
-    <t>r</t>
   </si>
   <si>
     <t>a</t>
@@ -95,13 +70,33 @@
   <si>
     <t>Piece i</t>
   </si>
+  <si>
+    <t>Computed constants</t>
+  </si>
+  <si>
+    <t>Fundamental constants</t>
+  </si>
+  <si>
+    <t>Acceleration (a) by subject position (A) and by piece</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="171" formatCode="0.0E+00"/>
+  </numFmts>
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -129,9 +124,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -204,7 +210,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$L$1</c:f>
+              <c:f>Sheet1!$Y$5</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -237,10 +243,10 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!$K$2:$K$34</c:f>
+              <c:f>Sheet1!$G$6:$G$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="33"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
                   <c:v>-1</c:v>
                 </c:pt>
@@ -285,48 +291,48 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$L$2:$L$34</c:f>
+              <c:f>Sheet1!$Y$6:$Y$18</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="33"/>
+                <c:formatCode>0.00E+00</c:formatCode>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>3.335251822770423E-11</c:v>
+                  <c:v>-3.335251822770423E-11</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5.0804486853651148E-11</c:v>
+                  <c:v>-5.0804486853651148E-11</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>-8.8824229300050502E-11</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-2.1222726695327648E-10</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-5.2030947489596425E-9</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-1.7667126090479272E-10</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3.5866034372416434E-25</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.7667126090479192E-10</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>5.2030947489596449E-9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2.122272669532765E-10</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>8.8824229300050502E-11</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>2.1222726695327648E-10</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>5.2030947489596425E-9</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>1.7667126090479272E-10</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>-3.5866034372416434E-25</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>-1.7667126090479192E-10</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>-5.2030947489596449E-9</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>-2.122272669532765E-10</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>-8.8824229300050502E-11</c:v>
-                </c:pt>
                 <c:pt idx="11">
-                  <c:v>-5.0804486853651142E-11</c:v>
+                  <c:v>5.0804486853651142E-11</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-3.335251822770423E-11</c:v>
+                  <c:v>3.335251822770423E-11</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -334,7 +340,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-CB87-4DC5-95CA-8C8AFD28112B}"/>
+              <c16:uniqueId val="{00000000-9CC4-47D5-9F27-EE1B5D9874D5}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -346,11 +352,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="2042428192"/>
-        <c:axId val="2042425312"/>
+        <c:axId val="336779119"/>
+        <c:axId val="336777199"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="2042428192"/>
+        <c:axId val="336779119"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="2"/>
@@ -409,13 +415,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2042425312"/>
+        <c:crossAx val="336777199"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
-        <c:majorUnit val="0.25"/>
+        <c:majorUnit val="1"/>
+        <c:minorUnit val="0.25"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="2042425312"/>
+        <c:axId val="336777199"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -435,7 +442,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0.00E+00" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -472,7 +479,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2042428192"/>
+        <c:crossAx val="336779119"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1088,23 +1095,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>133350</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>119062</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>200025</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>266700</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>4762</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1">
+        <xdr:cNvPr id="3" name="Chart 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0E82A5AB-D20A-DEBD-49A5-1C9511F395BB}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9A9AC302-02B5-356E-E4F6-F8D21A43CCF8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1442,405 +1449,1249 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0959997-E1B5-4FDD-A28A-D7F115F26C5F}">
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:AA19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.28515625" customWidth="1"/>
     <col min="2" max="2" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="2.7109375" customWidth="1"/>
+    <col min="3" max="3" width="2.85546875" customWidth="1"/>
     <col min="5" max="5" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="2.7109375" customWidth="1"/>
-    <col min="7" max="7" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="2.7109375" customWidth="1"/>
-    <col min="10" max="11" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.42578125" customWidth="1"/>
+    <col min="7" max="7" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="2.85546875" customWidth="1"/>
+    <col min="9" max="24" width="8" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="1">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
+      <c r="Q1" s="3"/>
+      <c r="R1" s="3"/>
+      <c r="S1" s="3"/>
+      <c r="T1" s="3"/>
+      <c r="U1" s="3"/>
+      <c r="V1" s="3"/>
+      <c r="W1" s="3"/>
+      <c r="X1" s="3"/>
+      <c r="Y1" s="3"/>
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+      <c r="T2" s="3"/>
+      <c r="U2" s="3"/>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
         <v>6.6742999999999994E-11</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <f>A6-A5</f>
+        <v>1</v>
+      </c>
+      <c r="E3" t="s">
         <v>5</v>
       </c>
-      <c r="D1">
-        <f>A4-A3</f>
+      <c r="H3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
         <v>1</v>
       </c>
-      <c r="E1" t="s">
+      <c r="K3">
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>3</v>
+      </c>
+      <c r="M3">
+        <v>4</v>
+      </c>
+      <c r="N3">
+        <v>5</v>
+      </c>
+      <c r="O3">
         <v>6</v>
       </c>
-      <c r="G1" t="s">
+      <c r="P3">
+        <v>7</v>
+      </c>
+      <c r="Q3">
+        <v>8</v>
+      </c>
+      <c r="R3">
+        <v>9</v>
+      </c>
+      <c r="S3">
+        <v>10</v>
+      </c>
+      <c r="T3">
         <v>11</v>
       </c>
-      <c r="H1" t="s">
-        <v>9</v>
-      </c>
-      <c r="J1" t="s">
-        <v>10</v>
-      </c>
-      <c r="K1" t="s">
-        <v>2</v>
-      </c>
-      <c r="L1" t="s">
-        <v>3</v>
+      <c r="U3">
+        <v>12</v>
+      </c>
+      <c r="V3">
+        <v>13</v>
+      </c>
+      <c r="W3">
+        <v>14</v>
+      </c>
+      <c r="X3">
+        <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <f>A2/A5</f>
-        <v>6.25E-2</v>
-      </c>
-      <c r="E2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <f t="shared" ref="H2:H18" si="0">$A$3+$D$1*(G2+0.5)/$A$5</f>
-        <v>3.125E-2</v>
-      </c>
-      <c r="J2">
-        <v>-1</v>
-      </c>
-      <c r="K2">
-        <f>J2-$A$3</f>
-        <v>-1</v>
-      </c>
-      <c r="L2" cm="1">
-        <f t="array" ref="L2">SUM(VALUE(IF(ISNUMBER(H:H),$A$1*$A$2*$D$2*SIGN(H:H-J2)/(H:H-J2)^2,0)))</f>
-        <v>3.335251822770423E-11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>0</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G3">
-        <f t="shared" ref="G3:G18" si="1">IF(G2+1&lt;$A$5,G2+1,0/0)</f>
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <f t="shared" si="0"/>
-        <v>9.375E-2</v>
-      </c>
-      <c r="J3">
-        <f>J2+(1/4)</f>
-        <v>-0.75</v>
-      </c>
-      <c r="K3">
-        <f t="shared" ref="K3:K14" si="2">J3-$A$3</f>
-        <v>-0.75</v>
-      </c>
-      <c r="L3" cm="1">
-        <f t="array" ref="L3">SUM(VALUE(IF(ISNUMBER(H:H),$A$1*$A$2*$D$2*SIGN(H:H-J3)/(H:H-J3)^2,0)))</f>
-        <v>5.0804486853651148E-11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1</v>
       </c>
       <c r="B4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <f>A4/A7</f>
+        <v>6.25E-2</v>
+      </c>
+      <c r="E4" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="G4">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="H4">
+      <c r="I4" s="7">
+        <f>$A$5+$D$3*(I3+0.5)/$A$7</f>
+        <v>3.125E-2</v>
+      </c>
+      <c r="J4" s="7">
+        <f t="shared" ref="J4:X4" si="0">$A$5+$D$3*(J3+0.5)/$A$7</f>
+        <v>9.375E-2</v>
+      </c>
+      <c r="K4" s="7">
         <f t="shared" si="0"/>
         <v>0.15625</v>
       </c>
-      <c r="J4">
-        <f t="shared" ref="J4:J10" si="3">J3+(1/4)</f>
-        <v>-0.5</v>
-      </c>
-      <c r="K4">
-        <f t="shared" si="2"/>
-        <v>-0.5</v>
-      </c>
-      <c r="L4" cm="1">
-        <f t="array" ref="L4">SUM(VALUE(IF(ISNUMBER(H:H),$A$1*$A$2*$D$2*SIGN(H:H-J4)/(H:H-J4)^2,0)))</f>
-        <v>8.8824229300050502E-11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>16</v>
-      </c>
-      <c r="B5" t="s">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="H5">
+      <c r="L4" s="7">
         <f t="shared" si="0"/>
         <v>0.21875</v>
       </c>
-      <c r="J5">
-        <f t="shared" si="3"/>
-        <v>-0.25</v>
-      </c>
-      <c r="K5">
+      <c r="M4" s="7">
+        <f t="shared" si="0"/>
+        <v>0.28125</v>
+      </c>
+      <c r="N4" s="7">
+        <f t="shared" si="0"/>
+        <v>0.34375</v>
+      </c>
+      <c r="O4" s="7">
+        <f t="shared" si="0"/>
+        <v>0.40625</v>
+      </c>
+      <c r="P4" s="7">
+        <f t="shared" si="0"/>
+        <v>0.46875</v>
+      </c>
+      <c r="Q4" s="7">
+        <f t="shared" si="0"/>
+        <v>0.53125</v>
+      </c>
+      <c r="R4" s="7">
+        <f t="shared" si="0"/>
+        <v>0.59375</v>
+      </c>
+      <c r="S4" s="7">
+        <f t="shared" si="0"/>
+        <v>0.65625</v>
+      </c>
+      <c r="T4" s="7">
+        <f t="shared" si="0"/>
+        <v>0.71875</v>
+      </c>
+      <c r="U4" s="7">
+        <f t="shared" si="0"/>
+        <v>0.78125</v>
+      </c>
+      <c r="V4" s="7">
+        <f t="shared" si="0"/>
+        <v>0.84375</v>
+      </c>
+      <c r="W4" s="7">
+        <f t="shared" si="0"/>
+        <v>0.90625</v>
+      </c>
+      <c r="X4" s="7">
+        <f t="shared" si="0"/>
+        <v>0.96875</v>
+      </c>
+      <c r="Z4" s="1"/>
+      <c r="AA4" s="1"/>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>0</v>
+      </c>
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y5" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z5" s="1"/>
+      <c r="AA5" s="1"/>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+      <c r="G6">
+        <v>-1</v>
+      </c>
+      <c r="I6" s="8">
+        <f>$A$3*$D$4*SIGN($G6-I$4)/($G6-I$4)^2</f>
+        <v>-3.9224536271808994E-12</v>
+      </c>
+      <c r="J6" s="8">
+        <f>$A$3*$D$4*SIGN($G6-J$4)/($G6-J$4)^2</f>
+        <v>-3.4869812244897956E-12</v>
+      </c>
+      <c r="K6" s="8">
+        <f>$A$3*$D$4*SIGN($G6-K$4)/($G6-K$4)^2</f>
+        <v>-3.1201986851716579E-12</v>
+      </c>
+      <c r="L6" s="8">
+        <f>$A$3*$D$4*SIGN($G6-L$4)/($G6-L$4)^2</f>
+        <v>-2.8083839579224193E-12</v>
+      </c>
+      <c r="M6" s="8">
+        <f>$A$3*$D$4*SIGN($G6-M$4)/($G6-M$4)^2</f>
+        <v>-2.5410779298036882E-12</v>
+      </c>
+      <c r="N6" s="8">
+        <f>$A$3*$D$4*SIGN($G6-N$4)/($G6-N$4)^2</f>
+        <v>-2.3101957815035153E-12</v>
+      </c>
+      <c r="O6" s="8">
+        <f>$A$3*$D$4*SIGN($G6-O$4)/($G6-O$4)^2</f>
+        <v>-2.1094083950617284E-12</v>
+      </c>
+      <c r="P6" s="8">
+        <f>$A$3*$D$4*SIGN($G6-P$4)/($G6-P$4)^2</f>
+        <v>-1.9337039384336801E-12</v>
+      </c>
+      <c r="Q6" s="8">
+        <f>$A$3*$D$4*SIGN($G6-Q$4)/($G6-Q$4)^2</f>
+        <v>-1.7790720533111202E-12</v>
+      </c>
+      <c r="R6" s="8">
+        <f>$A$3*$D$4*SIGN($G6-R$4)/($G6-R$4)^2</f>
+        <v>-1.6422729719338714E-12</v>
+      </c>
+      <c r="S6" s="8">
+        <f>$A$3*$D$4*SIGN($G6-S$4)/($G6-S$4)^2</f>
+        <v>-1.5206664293342826E-12</v>
+      </c>
+      <c r="T6" s="8">
+        <f>$A$3*$D$4*SIGN($G6-T$4)/($G6-T$4)^2</f>
+        <v>-1.4120833057851238E-12</v>
+      </c>
+      <c r="U6" s="8">
+        <f>$A$3*$D$4*SIGN($G6-U$4)/($G6-U$4)^2</f>
+        <v>-1.3147282240689442E-12</v>
+      </c>
+      <c r="V6" s="8">
+        <f>$A$3*$D$4*SIGN($G6-V$4)/($G6-V$4)^2</f>
+        <v>-1.2271048549267451E-12</v>
+      </c>
+      <c r="W6" s="8">
+        <f>$A$3*$D$4*SIGN($G6-W$4)/($G6-W$4)^2</f>
+        <v>-1.1479580757860789E-12</v>
+      </c>
+      <c r="X6" s="8">
+        <f>$A$3*$D$4*SIGN($G6-X$4)/($G6-X$4)^2</f>
+        <v>-1.0762287729906776E-12</v>
+      </c>
+      <c r="Y6" s="6">
+        <f>SUM(I6:X6)</f>
+        <v>-3.335251822770423E-11</v>
+      </c>
+      <c r="Z6" s="1"/>
+      <c r="AA6" s="1"/>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>16</v>
+      </c>
+      <c r="B7" t="s">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <f>G6+(1/4)</f>
+        <v>-0.75</v>
+      </c>
+      <c r="I7" s="8">
+        <f>$A$3*$D$4*SIGN($G7-I$4)/($G7-I$4)^2</f>
+        <v>-6.8344831999999996E-12</v>
+      </c>
+      <c r="J7" s="8">
+        <f>$A$3*$D$4*SIGN($G7-J$4)/($G7-J$4)^2</f>
+        <v>-5.8594677640603565E-12</v>
+      </c>
+      <c r="K7" s="8">
+        <f>$A$3*$D$4*SIGN($G7-K$4)/($G7-K$4)^2</f>
+        <v>-5.0791343638525559E-12</v>
+      </c>
+      <c r="L7" s="8">
+        <f>$A$3*$D$4*SIGN($G7-L$4)/($G7-L$4)^2</f>
+        <v>-4.4449032258064514E-12</v>
+      </c>
+      <c r="M7" s="8">
+        <f>$A$3*$D$4*SIGN($G7-M$4)/($G7-M$4)^2</f>
+        <v>-3.9224536271808994E-12</v>
+      </c>
+      <c r="N7" s="8">
+        <f>$A$3*$D$4*SIGN($G7-N$4)/($G7-N$4)^2</f>
+        <v>-3.4869812244897956E-12</v>
+      </c>
+      <c r="O7" s="8">
+        <f>$A$3*$D$4*SIGN($G7-O$4)/($G7-O$4)^2</f>
+        <v>-3.1201986851716579E-12</v>
+      </c>
+      <c r="P7" s="8">
+        <f>$A$3*$D$4*SIGN($G7-P$4)/($G7-P$4)^2</f>
+        <v>-2.8083839579224193E-12</v>
+      </c>
+      <c r="Q7" s="8">
+        <f>$A$3*$D$4*SIGN($G7-Q$4)/($G7-Q$4)^2</f>
+        <v>-2.5410779298036882E-12</v>
+      </c>
+      <c r="R7" s="8">
+        <f>$A$3*$D$4*SIGN($G7-R$4)/($G7-R$4)^2</f>
+        <v>-2.3101957815035153E-12</v>
+      </c>
+      <c r="S7" s="8">
+        <f>$A$3*$D$4*SIGN($G7-S$4)/($G7-S$4)^2</f>
+        <v>-2.1094083950617284E-12</v>
+      </c>
+      <c r="T7" s="8">
+        <f>$A$3*$D$4*SIGN($G7-T$4)/($G7-T$4)^2</f>
+        <v>-1.9337039384336801E-12</v>
+      </c>
+      <c r="U7" s="8">
+        <f>$A$3*$D$4*SIGN($G7-U$4)/($G7-U$4)^2</f>
+        <v>-1.7790720533111202E-12</v>
+      </c>
+      <c r="V7" s="8">
+        <f>$A$3*$D$4*SIGN($G7-V$4)/($G7-V$4)^2</f>
+        <v>-1.6422729719338714E-12</v>
+      </c>
+      <c r="W7" s="8">
+        <f>$A$3*$D$4*SIGN($G7-W$4)/($G7-W$4)^2</f>
+        <v>-1.5206664293342826E-12</v>
+      </c>
+      <c r="X7" s="8">
+        <f>$A$3*$D$4*SIGN($G7-X$4)/($G7-X$4)^2</f>
+        <v>-1.4120833057851238E-12</v>
+      </c>
+      <c r="Y7" s="6">
+        <f t="shared" ref="Y7:Y18" si="1">SUM(I7:X7)</f>
+        <v>-5.0804486853651148E-11</v>
+      </c>
+      <c r="Z7" s="1"/>
+      <c r="AA7" s="1"/>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="G8">
+        <f t="shared" ref="G8:G18" si="2">G7+(1/4)</f>
+        <v>-0.5</v>
+      </c>
+      <c r="I8" s="8">
+        <f>$A$3*$D$4*SIGN($G8-I$4)/($G8-I$4)^2</f>
+        <v>-1.4780456747404844E-11</v>
+      </c>
+      <c r="J8" s="8">
+        <f>$A$3*$D$4*SIGN($G8-J$4)/($G8-J$4)^2</f>
+        <v>-1.1832554016620497E-11</v>
+      </c>
+      <c r="K8" s="8">
+        <f>$A$3*$D$4*SIGN($G8-K$4)/($G8-K$4)^2</f>
+        <v>-9.6860589569160981E-12</v>
+      </c>
+      <c r="L8" s="8">
+        <f>$A$3*$D$4*SIGN($G8-L$4)/($G8-L$4)^2</f>
+        <v>-8.0747674858223054E-12</v>
+      </c>
+      <c r="M8" s="8">
+        <f>$A$3*$D$4*SIGN($G8-M$4)/($G8-M$4)^2</f>
+        <v>-6.8344831999999996E-12</v>
+      </c>
+      <c r="N8" s="8">
+        <f>$A$3*$D$4*SIGN($G8-N$4)/($G8-N$4)^2</f>
+        <v>-5.8594677640603565E-12</v>
+      </c>
+      <c r="O8" s="8">
+        <f>$A$3*$D$4*SIGN($G8-O$4)/($G8-O$4)^2</f>
+        <v>-5.0791343638525559E-12</v>
+      </c>
+      <c r="P8" s="8">
+        <f>$A$3*$D$4*SIGN($G8-P$4)/($G8-P$4)^2</f>
+        <v>-4.4449032258064514E-12</v>
+      </c>
+      <c r="Q8" s="8">
+        <f>$A$3*$D$4*SIGN($G8-Q$4)/($G8-Q$4)^2</f>
+        <v>-3.9224536271808994E-12</v>
+      </c>
+      <c r="R8" s="8">
+        <f>$A$3*$D$4*SIGN($G8-R$4)/($G8-R$4)^2</f>
+        <v>-3.4869812244897956E-12</v>
+      </c>
+      <c r="S8" s="8">
+        <f>$A$3*$D$4*SIGN($G8-S$4)/($G8-S$4)^2</f>
+        <v>-3.1201986851716579E-12</v>
+      </c>
+      <c r="T8" s="8">
+        <f>$A$3*$D$4*SIGN($G8-T$4)/($G8-T$4)^2</f>
+        <v>-2.8083839579224193E-12</v>
+      </c>
+      <c r="U8" s="8">
+        <f>$A$3*$D$4*SIGN($G8-U$4)/($G8-U$4)^2</f>
+        <v>-2.5410779298036882E-12</v>
+      </c>
+      <c r="V8" s="8">
+        <f>$A$3*$D$4*SIGN($G8-V$4)/($G8-V$4)^2</f>
+        <v>-2.3101957815035153E-12</v>
+      </c>
+      <c r="W8" s="8">
+        <f>$A$3*$D$4*SIGN($G8-W$4)/($G8-W$4)^2</f>
+        <v>-2.1094083950617284E-12</v>
+      </c>
+      <c r="X8" s="8">
+        <f>$A$3*$D$4*SIGN($G8-X$4)/($G8-X$4)^2</f>
+        <v>-1.9337039384336801E-12</v>
+      </c>
+      <c r="Y8" s="6">
+        <f t="shared" si="1"/>
+        <v>-8.8824229300050502E-11</v>
+      </c>
+      <c r="Z8" s="1"/>
+      <c r="AA8" s="1"/>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="G9">
         <f t="shared" si="2"/>
         <v>-0.25</v>
       </c>
-      <c r="L5" cm="1">
-        <f t="array" ref="L5">SUM(VALUE(IF(ISNUMBER(H:H),$A$1*$A$2*$D$2*SIGN(H:H-J5)/(H:H-J5)^2,0)))</f>
-        <v>2.1222726695327648E-10</v>
-      </c>
+      <c r="I9" s="8">
+        <f>$A$3*$D$4*SIGN($G9-I$4)/($G9-I$4)^2</f>
+        <v>-5.2735209876543207E-11</v>
+      </c>
+      <c r="J9" s="8">
+        <f>$A$3*$D$4*SIGN($G9-J$4)/($G9-J$4)^2</f>
+        <v>-3.5302082644628097E-11</v>
+      </c>
+      <c r="K9" s="8">
+        <f>$A$3*$D$4*SIGN($G9-K$4)/($G9-K$4)^2</f>
+        <v>-2.5275455621301774E-11</v>
+      </c>
+      <c r="L9" s="8">
+        <f>$A$3*$D$4*SIGN($G9-L$4)/($G9-L$4)^2</f>
+        <v>-1.8984675555555553E-11</v>
+      </c>
+      <c r="M9" s="8">
+        <f>$A$3*$D$4*SIGN($G9-M$4)/($G9-M$4)^2</f>
+        <v>-1.4780456747404844E-11</v>
+      </c>
+      <c r="N9" s="8">
+        <f>$A$3*$D$4*SIGN($G9-N$4)/($G9-N$4)^2</f>
+        <v>-1.1832554016620497E-11</v>
+      </c>
+      <c r="O9" s="8">
+        <f>$A$3*$D$4*SIGN($G9-O$4)/($G9-O$4)^2</f>
+        <v>-9.6860589569160981E-12</v>
+      </c>
+      <c r="P9" s="8">
+        <f>$A$3*$D$4*SIGN($G9-P$4)/($G9-P$4)^2</f>
+        <v>-8.0747674858223054E-12</v>
+      </c>
+      <c r="Q9" s="8">
+        <f>$A$3*$D$4*SIGN($G9-Q$4)/($G9-Q$4)^2</f>
+        <v>-6.8344831999999996E-12</v>
+      </c>
+      <c r="R9" s="8">
+        <f>$A$3*$D$4*SIGN($G9-R$4)/($G9-R$4)^2</f>
+        <v>-5.8594677640603565E-12</v>
+      </c>
+      <c r="S9" s="8">
+        <f>$A$3*$D$4*SIGN($G9-S$4)/($G9-S$4)^2</f>
+        <v>-5.0791343638525559E-12</v>
+      </c>
+      <c r="T9" s="8">
+        <f>$A$3*$D$4*SIGN($G9-T$4)/($G9-T$4)^2</f>
+        <v>-4.4449032258064514E-12</v>
+      </c>
+      <c r="U9" s="8">
+        <f>$A$3*$D$4*SIGN($G9-U$4)/($G9-U$4)^2</f>
+        <v>-3.9224536271808994E-12</v>
+      </c>
+      <c r="V9" s="8">
+        <f>$A$3*$D$4*SIGN($G9-V$4)/($G9-V$4)^2</f>
+        <v>-3.4869812244897956E-12</v>
+      </c>
+      <c r="W9" s="8">
+        <f>$A$3*$D$4*SIGN($G9-W$4)/($G9-W$4)^2</f>
+        <v>-3.1201986851716579E-12</v>
+      </c>
+      <c r="X9" s="8">
+        <f>$A$3*$D$4*SIGN($G9-X$4)/($G9-X$4)^2</f>
+        <v>-2.8083839579224193E-12</v>
+      </c>
+      <c r="Y9" s="6">
+        <f t="shared" si="1"/>
+        <v>-2.1222726695327648E-10</v>
+      </c>
+      <c r="Z9" s="1"/>
+      <c r="AA9" s="1"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="G6">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="H6">
-        <f t="shared" si="0"/>
-        <v>0.28125</v>
-      </c>
-      <c r="J6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K6">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="G10">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L6" cm="1">
-        <f t="array" ref="L6">SUM(VALUE(IF(ISNUMBER(H:H),$A$1*$A$2*$D$2*SIGN(H:H-J6)/(H:H-J6)^2,0)))</f>
-        <v>5.2030947489596425E-9</v>
-      </c>
+      <c r="I10" s="8">
+        <f>$A$3*$D$4*SIGN($G10-I$4)/($G10-I$4)^2</f>
+        <v>-4.2715519999999996E-9</v>
+      </c>
+      <c r="J10" s="8">
+        <f>$A$3*$D$4*SIGN($G10-J$4)/($G10-J$4)^2</f>
+        <v>-4.7461688888888888E-10</v>
+      </c>
+      <c r="K10" s="8">
+        <f>$A$3*$D$4*SIGN($G10-K$4)/($G10-K$4)^2</f>
+        <v>-1.7086207999999998E-10</v>
+      </c>
+      <c r="L10" s="8">
+        <f>$A$3*$D$4*SIGN($G10-L$4)/($G10-L$4)^2</f>
+        <v>-8.717453061224489E-11</v>
+      </c>
+      <c r="M10" s="8">
+        <f>$A$3*$D$4*SIGN($G10-M$4)/($G10-M$4)^2</f>
+        <v>-5.2735209876543207E-11</v>
+      </c>
+      <c r="N10" s="8">
+        <f>$A$3*$D$4*SIGN($G10-N$4)/($G10-N$4)^2</f>
+        <v>-3.5302082644628097E-11</v>
+      </c>
+      <c r="O10" s="8">
+        <f>$A$3*$D$4*SIGN($G10-O$4)/($G10-O$4)^2</f>
+        <v>-2.5275455621301774E-11</v>
+      </c>
+      <c r="P10" s="8">
+        <f>$A$3*$D$4*SIGN($G10-P$4)/($G10-P$4)^2</f>
+        <v>-1.8984675555555553E-11</v>
+      </c>
+      <c r="Q10" s="8">
+        <f>$A$3*$D$4*SIGN($G10-Q$4)/($G10-Q$4)^2</f>
+        <v>-1.4780456747404844E-11</v>
+      </c>
+      <c r="R10" s="8">
+        <f>$A$3*$D$4*SIGN($G10-R$4)/($G10-R$4)^2</f>
+        <v>-1.1832554016620497E-11</v>
+      </c>
+      <c r="S10" s="8">
+        <f>$A$3*$D$4*SIGN($G10-S$4)/($G10-S$4)^2</f>
+        <v>-9.6860589569160981E-12</v>
+      </c>
+      <c r="T10" s="8">
+        <f>$A$3*$D$4*SIGN($G10-T$4)/($G10-T$4)^2</f>
+        <v>-8.0747674858223054E-12</v>
+      </c>
+      <c r="U10" s="8">
+        <f>$A$3*$D$4*SIGN($G10-U$4)/($G10-U$4)^2</f>
+        <v>-6.8344831999999996E-12</v>
+      </c>
+      <c r="V10" s="8">
+        <f>$A$3*$D$4*SIGN($G10-V$4)/($G10-V$4)^2</f>
+        <v>-5.8594677640603565E-12</v>
+      </c>
+      <c r="W10" s="8">
+        <f>$A$3*$D$4*SIGN($G10-W$4)/($G10-W$4)^2</f>
+        <v>-5.0791343638525559E-12</v>
+      </c>
+      <c r="X10" s="8">
+        <f>$A$3*$D$4*SIGN($G10-X$4)/($G10-X$4)^2</f>
+        <v>-4.4449032258064514E-12</v>
+      </c>
+      <c r="Y10" s="6">
+        <f t="shared" si="1"/>
+        <v>-5.2030947489596425E-9</v>
+      </c>
+      <c r="Z10" s="1"/>
+      <c r="AA10" s="1"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="G7">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="H7">
-        <f t="shared" si="0"/>
-        <v>0.34375</v>
-      </c>
-      <c r="J7">
-        <f t="shared" si="3"/>
-        <v>0.25</v>
-      </c>
-      <c r="K7">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="G11">
         <f t="shared" si="2"/>
         <v>0.25</v>
       </c>
-      <c r="L7" cm="1">
-        <f t="array" ref="L7">SUM(VALUE(IF(ISNUMBER(H:H),$A$1*$A$2*$D$2*SIGN(H:H-J7)/(H:H-J7)^2,0)))</f>
-        <v>1.7667126090479272E-10</v>
-      </c>
+      <c r="I11" s="8">
+        <f>$A$3*$D$4*SIGN($G11-I$4)/($G11-I$4)^2</f>
+        <v>8.717453061224489E-11</v>
+      </c>
+      <c r="J11" s="8">
+        <f>$A$3*$D$4*SIGN($G11-J$4)/($G11-J$4)^2</f>
+        <v>1.7086207999999998E-10</v>
+      </c>
+      <c r="K11" s="8">
+        <f>$A$3*$D$4*SIGN($G11-K$4)/($G11-K$4)^2</f>
+        <v>4.7461688888888888E-10</v>
+      </c>
+      <c r="L11" s="8">
+        <f>$A$3*$D$4*SIGN($G11-L$4)/($G11-L$4)^2</f>
+        <v>4.2715519999999996E-9</v>
+      </c>
+      <c r="M11" s="8">
+        <f>$A$3*$D$4*SIGN($G11-M$4)/($G11-M$4)^2</f>
+        <v>-4.2715519999999996E-9</v>
+      </c>
+      <c r="N11" s="8">
+        <f>$A$3*$D$4*SIGN($G11-N$4)/($G11-N$4)^2</f>
+        <v>-4.7461688888888888E-10</v>
+      </c>
+      <c r="O11" s="8">
+        <f>$A$3*$D$4*SIGN($G11-O$4)/($G11-O$4)^2</f>
+        <v>-1.7086207999999998E-10</v>
+      </c>
+      <c r="P11" s="8">
+        <f>$A$3*$D$4*SIGN($G11-P$4)/($G11-P$4)^2</f>
+        <v>-8.717453061224489E-11</v>
+      </c>
+      <c r="Q11" s="8">
+        <f>$A$3*$D$4*SIGN($G11-Q$4)/($G11-Q$4)^2</f>
+        <v>-5.2735209876543207E-11</v>
+      </c>
+      <c r="R11" s="8">
+        <f>$A$3*$D$4*SIGN($G11-R$4)/($G11-R$4)^2</f>
+        <v>-3.5302082644628097E-11</v>
+      </c>
+      <c r="S11" s="8">
+        <f>$A$3*$D$4*SIGN($G11-S$4)/($G11-S$4)^2</f>
+        <v>-2.5275455621301774E-11</v>
+      </c>
+      <c r="T11" s="8">
+        <f>$A$3*$D$4*SIGN($G11-T$4)/($G11-T$4)^2</f>
+        <v>-1.8984675555555553E-11</v>
+      </c>
+      <c r="U11" s="8">
+        <f>$A$3*$D$4*SIGN($G11-U$4)/($G11-U$4)^2</f>
+        <v>-1.4780456747404844E-11</v>
+      </c>
+      <c r="V11" s="8">
+        <f>$A$3*$D$4*SIGN($G11-V$4)/($G11-V$4)^2</f>
+        <v>-1.1832554016620497E-11</v>
+      </c>
+      <c r="W11" s="8">
+        <f>$A$3*$D$4*SIGN($G11-W$4)/($G11-W$4)^2</f>
+        <v>-9.6860589569160981E-12</v>
+      </c>
+      <c r="X11" s="8">
+        <f>$A$3*$D$4*SIGN($G11-X$4)/($G11-X$4)^2</f>
+        <v>-8.0747674858223054E-12</v>
+      </c>
+      <c r="Y11" s="6">
+        <f t="shared" si="1"/>
+        <v>-1.7667126090479272E-10</v>
+      </c>
+      <c r="Z11" s="1"/>
+      <c r="AA11" s="1"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="G8">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="H8">
-        <f t="shared" si="0"/>
-        <v>0.40625</v>
-      </c>
-      <c r="J8">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
-      </c>
-      <c r="K8">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="G12">
         <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
-      <c r="L8" cm="1">
-        <f t="array" ref="L8">SUM(VALUE(IF(ISNUMBER(H:H),$A$1*$A$2*$D$2*SIGN(H:H-J8)/(H:H-J8)^2,0)))</f>
-        <v>-3.5866034372416434E-25</v>
-      </c>
+      <c r="I12" s="8">
+        <f>$A$3*$D$4*SIGN($G12-I$4)/($G12-I$4)^2</f>
+        <v>1.8984675555555553E-11</v>
+      </c>
+      <c r="J12" s="8">
+        <f>$A$3*$D$4*SIGN($G12-J$4)/($G12-J$4)^2</f>
+        <v>2.5275455621301774E-11</v>
+      </c>
+      <c r="K12" s="8">
+        <f>$A$3*$D$4*SIGN($G12-K$4)/($G12-K$4)^2</f>
+        <v>3.5302082644628097E-11</v>
+      </c>
+      <c r="L12" s="8">
+        <f>$A$3*$D$4*SIGN($G12-L$4)/($G12-L$4)^2</f>
+        <v>5.2735209876543207E-11</v>
+      </c>
+      <c r="M12" s="8">
+        <f>$A$3*$D$4*SIGN($G12-M$4)/($G12-M$4)^2</f>
+        <v>8.717453061224489E-11</v>
+      </c>
+      <c r="N12" s="8">
+        <f>$A$3*$D$4*SIGN($G12-N$4)/($G12-N$4)^2</f>
+        <v>1.7086207999999998E-10</v>
+      </c>
+      <c r="O12" s="8">
+        <f>$A$3*$D$4*SIGN($G12-O$4)/($G12-O$4)^2</f>
+        <v>4.7461688888888888E-10</v>
+      </c>
+      <c r="P12" s="8">
+        <f>$A$3*$D$4*SIGN($G12-P$4)/($G12-P$4)^2</f>
+        <v>4.2715519999999996E-9</v>
+      </c>
+      <c r="Q12" s="8">
+        <f>$A$3*$D$4*SIGN($G12-Q$4)/($G12-Q$4)^2</f>
+        <v>-4.2715519999999996E-9</v>
+      </c>
+      <c r="R12" s="8">
+        <f>$A$3*$D$4*SIGN($G12-R$4)/($G12-R$4)^2</f>
+        <v>-4.7461688888888888E-10</v>
+      </c>
+      <c r="S12" s="8">
+        <f>$A$3*$D$4*SIGN($G12-S$4)/($G12-S$4)^2</f>
+        <v>-1.7086207999999998E-10</v>
+      </c>
+      <c r="T12" s="8">
+        <f>$A$3*$D$4*SIGN($G12-T$4)/($G12-T$4)^2</f>
+        <v>-8.717453061224489E-11</v>
+      </c>
+      <c r="U12" s="8">
+        <f>$A$3*$D$4*SIGN($G12-U$4)/($G12-U$4)^2</f>
+        <v>-5.2735209876543207E-11</v>
+      </c>
+      <c r="V12" s="8">
+        <f>$A$3*$D$4*SIGN($G12-V$4)/($G12-V$4)^2</f>
+        <v>-3.5302082644628097E-11</v>
+      </c>
+      <c r="W12" s="8">
+        <f>$A$3*$D$4*SIGN($G12-W$4)/($G12-W$4)^2</f>
+        <v>-2.5275455621301774E-11</v>
+      </c>
+      <c r="X12" s="8">
+        <f>$A$3*$D$4*SIGN($G12-X$4)/($G12-X$4)^2</f>
+        <v>-1.8984675555555553E-11</v>
+      </c>
+      <c r="Y12" s="6">
+        <f t="shared" si="1"/>
+        <v>3.5866034372416434E-25</v>
+      </c>
+      <c r="Z12" s="1"/>
+      <c r="AA12" s="1"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="G9">
-        <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-      <c r="H9">
-        <f t="shared" si="0"/>
-        <v>0.46875</v>
-      </c>
-      <c r="J9">
-        <f t="shared" si="3"/>
-        <v>0.75</v>
-      </c>
-      <c r="K9">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="G13">
         <f t="shared" si="2"/>
         <v>0.75</v>
       </c>
-      <c r="L9" cm="1">
-        <f t="array" ref="L9">SUM(VALUE(IF(ISNUMBER(H:H),$A$1*$A$2*$D$2*SIGN(H:H-J9)/(H:H-J9)^2,0)))</f>
-        <v>-1.7667126090479192E-10</v>
-      </c>
+      <c r="I13" s="8">
+        <f>$A$3*$D$4*SIGN($G13-I$4)/($G13-I$4)^2</f>
+        <v>8.0747674858223054E-12</v>
+      </c>
+      <c r="J13" s="8">
+        <f>$A$3*$D$4*SIGN($G13-J$4)/($G13-J$4)^2</f>
+        <v>9.6860589569160981E-12</v>
+      </c>
+      <c r="K13" s="8">
+        <f>$A$3*$D$4*SIGN($G13-K$4)/($G13-K$4)^2</f>
+        <v>1.1832554016620497E-11</v>
+      </c>
+      <c r="L13" s="8">
+        <f>$A$3*$D$4*SIGN($G13-L$4)/($G13-L$4)^2</f>
+        <v>1.4780456747404844E-11</v>
+      </c>
+      <c r="M13" s="8">
+        <f>$A$3*$D$4*SIGN($G13-M$4)/($G13-M$4)^2</f>
+        <v>1.8984675555555553E-11</v>
+      </c>
+      <c r="N13" s="8">
+        <f>$A$3*$D$4*SIGN($G13-N$4)/($G13-N$4)^2</f>
+        <v>2.5275455621301774E-11</v>
+      </c>
+      <c r="O13" s="8">
+        <f>$A$3*$D$4*SIGN($G13-O$4)/($G13-O$4)^2</f>
+        <v>3.5302082644628097E-11</v>
+      </c>
+      <c r="P13" s="8">
+        <f>$A$3*$D$4*SIGN($G13-P$4)/($G13-P$4)^2</f>
+        <v>5.2735209876543207E-11</v>
+      </c>
+      <c r="Q13" s="8">
+        <f>$A$3*$D$4*SIGN($G13-Q$4)/($G13-Q$4)^2</f>
+        <v>8.717453061224489E-11</v>
+      </c>
+      <c r="R13" s="8">
+        <f>$A$3*$D$4*SIGN($G13-R$4)/($G13-R$4)^2</f>
+        <v>1.7086207999999998E-10</v>
+      </c>
+      <c r="S13" s="8">
+        <f>$A$3*$D$4*SIGN($G13-S$4)/($G13-S$4)^2</f>
+        <v>4.7461688888888888E-10</v>
+      </c>
+      <c r="T13" s="8">
+        <f>$A$3*$D$4*SIGN($G13-T$4)/($G13-T$4)^2</f>
+        <v>4.2715519999999996E-9</v>
+      </c>
+      <c r="U13" s="8">
+        <f>$A$3*$D$4*SIGN($G13-U$4)/($G13-U$4)^2</f>
+        <v>-4.2715519999999996E-9</v>
+      </c>
+      <c r="V13" s="8">
+        <f>$A$3*$D$4*SIGN($G13-V$4)/($G13-V$4)^2</f>
+        <v>-4.7461688888888888E-10</v>
+      </c>
+      <c r="W13" s="8">
+        <f>$A$3*$D$4*SIGN($G13-W$4)/($G13-W$4)^2</f>
+        <v>-1.7086207999999998E-10</v>
+      </c>
+      <c r="X13" s="8">
+        <f>$A$3*$D$4*SIGN($G13-X$4)/($G13-X$4)^2</f>
+        <v>-8.717453061224489E-11</v>
+      </c>
+      <c r="Y13" s="6">
+        <f t="shared" si="1"/>
+        <v>1.7667126090479192E-10</v>
+      </c>
+      <c r="Z13" s="1"/>
+      <c r="AA13" s="1"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="G10">
-        <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="H10">
-        <f t="shared" si="0"/>
-        <v>0.53125</v>
-      </c>
-      <c r="J10">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="K10">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="G14">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="L10" cm="1">
-        <f t="array" ref="L10">SUM(VALUE(IF(ISNUMBER(H:H),$A$1*$A$2*$D$2*SIGN(H:H-J10)/(H:H-J10)^2,0)))</f>
-        <v>-5.2030947489596449E-9</v>
-      </c>
+      <c r="I14" s="8">
+        <f>$A$3*$D$4*SIGN($G14-I$4)/($G14-I$4)^2</f>
+        <v>4.4449032258064514E-12</v>
+      </c>
+      <c r="J14" s="8">
+        <f>$A$3*$D$4*SIGN($G14-J$4)/($G14-J$4)^2</f>
+        <v>5.0791343638525559E-12</v>
+      </c>
+      <c r="K14" s="8">
+        <f>$A$3*$D$4*SIGN($G14-K$4)/($G14-K$4)^2</f>
+        <v>5.8594677640603565E-12</v>
+      </c>
+      <c r="L14" s="8">
+        <f>$A$3*$D$4*SIGN($G14-L$4)/($G14-L$4)^2</f>
+        <v>6.8344831999999996E-12</v>
+      </c>
+      <c r="M14" s="8">
+        <f>$A$3*$D$4*SIGN($G14-M$4)/($G14-M$4)^2</f>
+        <v>8.0747674858223054E-12</v>
+      </c>
+      <c r="N14" s="8">
+        <f>$A$3*$D$4*SIGN($G14-N$4)/($G14-N$4)^2</f>
+        <v>9.6860589569160981E-12</v>
+      </c>
+      <c r="O14" s="8">
+        <f>$A$3*$D$4*SIGN($G14-O$4)/($G14-O$4)^2</f>
+        <v>1.1832554016620497E-11</v>
+      </c>
+      <c r="P14" s="8">
+        <f>$A$3*$D$4*SIGN($G14-P$4)/($G14-P$4)^2</f>
+        <v>1.4780456747404844E-11</v>
+      </c>
+      <c r="Q14" s="8">
+        <f>$A$3*$D$4*SIGN($G14-Q$4)/($G14-Q$4)^2</f>
+        <v>1.8984675555555553E-11</v>
+      </c>
+      <c r="R14" s="8">
+        <f>$A$3*$D$4*SIGN($G14-R$4)/($G14-R$4)^2</f>
+        <v>2.5275455621301774E-11</v>
+      </c>
+      <c r="S14" s="8">
+        <f>$A$3*$D$4*SIGN($G14-S$4)/($G14-S$4)^2</f>
+        <v>3.5302082644628097E-11</v>
+      </c>
+      <c r="T14" s="8">
+        <f>$A$3*$D$4*SIGN($G14-T$4)/($G14-T$4)^2</f>
+        <v>5.2735209876543207E-11</v>
+      </c>
+      <c r="U14" s="8">
+        <f>$A$3*$D$4*SIGN($G14-U$4)/($G14-U$4)^2</f>
+        <v>8.717453061224489E-11</v>
+      </c>
+      <c r="V14" s="8">
+        <f>$A$3*$D$4*SIGN($G14-V$4)/($G14-V$4)^2</f>
+        <v>1.7086207999999998E-10</v>
+      </c>
+      <c r="W14" s="8">
+        <f>$A$3*$D$4*SIGN($G14-W$4)/($G14-W$4)^2</f>
+        <v>4.7461688888888888E-10</v>
+      </c>
+      <c r="X14" s="8">
+        <f>$A$3*$D$4*SIGN($G14-X$4)/($G14-X$4)^2</f>
+        <v>4.2715519999999996E-9</v>
+      </c>
+      <c r="Y14" s="6">
+        <f t="shared" si="1"/>
+        <v>5.2030947489596449E-9</v>
+      </c>
+      <c r="Z14" s="1"/>
+      <c r="AA14" s="1"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="G11">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="H11">
-        <f t="shared" si="0"/>
-        <v>0.59375</v>
-      </c>
-      <c r="J11">
-        <f t="shared" ref="J11:J14" si="4">J10+(1/4)</f>
-        <v>1.25</v>
-      </c>
-      <c r="K11">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="G15">
         <f t="shared" si="2"/>
         <v>1.25</v>
       </c>
-      <c r="L11" cm="1">
-        <f t="array" ref="L11">SUM(VALUE(IF(ISNUMBER(H:H),$A$1*$A$2*$D$2*SIGN(H:H-J11)/(H:H-J11)^2,0)))</f>
-        <v>-2.122272669532765E-10</v>
-      </c>
+      <c r="I15" s="8">
+        <f>$A$3*$D$4*SIGN($G15-I$4)/($G15-I$4)^2</f>
+        <v>2.8083839579224193E-12</v>
+      </c>
+      <c r="J15" s="8">
+        <f>$A$3*$D$4*SIGN($G15-J$4)/($G15-J$4)^2</f>
+        <v>3.1201986851716579E-12</v>
+      </c>
+      <c r="K15" s="8">
+        <f>$A$3*$D$4*SIGN($G15-K$4)/($G15-K$4)^2</f>
+        <v>3.4869812244897956E-12</v>
+      </c>
+      <c r="L15" s="8">
+        <f>$A$3*$D$4*SIGN($G15-L$4)/($G15-L$4)^2</f>
+        <v>3.9224536271808994E-12</v>
+      </c>
+      <c r="M15" s="8">
+        <f>$A$3*$D$4*SIGN($G15-M$4)/($G15-M$4)^2</f>
+        <v>4.4449032258064514E-12</v>
+      </c>
+      <c r="N15" s="8">
+        <f>$A$3*$D$4*SIGN($G15-N$4)/($G15-N$4)^2</f>
+        <v>5.0791343638525559E-12</v>
+      </c>
+      <c r="O15" s="8">
+        <f>$A$3*$D$4*SIGN($G15-O$4)/($G15-O$4)^2</f>
+        <v>5.8594677640603565E-12</v>
+      </c>
+      <c r="P15" s="8">
+        <f>$A$3*$D$4*SIGN($G15-P$4)/($G15-P$4)^2</f>
+        <v>6.8344831999999996E-12</v>
+      </c>
+      <c r="Q15" s="8">
+        <f>$A$3*$D$4*SIGN($G15-Q$4)/($G15-Q$4)^2</f>
+        <v>8.0747674858223054E-12</v>
+      </c>
+      <c r="R15" s="8">
+        <f>$A$3*$D$4*SIGN($G15-R$4)/($G15-R$4)^2</f>
+        <v>9.6860589569160981E-12</v>
+      </c>
+      <c r="S15" s="8">
+        <f>$A$3*$D$4*SIGN($G15-S$4)/($G15-S$4)^2</f>
+        <v>1.1832554016620497E-11</v>
+      </c>
+      <c r="T15" s="8">
+        <f>$A$3*$D$4*SIGN($G15-T$4)/($G15-T$4)^2</f>
+        <v>1.4780456747404844E-11</v>
+      </c>
+      <c r="U15" s="8">
+        <f>$A$3*$D$4*SIGN($G15-U$4)/($G15-U$4)^2</f>
+        <v>1.8984675555555553E-11</v>
+      </c>
+      <c r="V15" s="8">
+        <f>$A$3*$D$4*SIGN($G15-V$4)/($G15-V$4)^2</f>
+        <v>2.5275455621301774E-11</v>
+      </c>
+      <c r="W15" s="8">
+        <f>$A$3*$D$4*SIGN($G15-W$4)/($G15-W$4)^2</f>
+        <v>3.5302082644628097E-11</v>
+      </c>
+      <c r="X15" s="8">
+        <f>$A$3*$D$4*SIGN($G15-X$4)/($G15-X$4)^2</f>
+        <v>5.2735209876543207E-11</v>
+      </c>
+      <c r="Y15" s="6">
+        <f t="shared" si="1"/>
+        <v>2.122272669532765E-10</v>
+      </c>
+      <c r="Z15" s="1"/>
+      <c r="AA15" s="1"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="G12">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="H12">
-        <f t="shared" si="0"/>
-        <v>0.65625</v>
-      </c>
-      <c r="J12">
-        <f t="shared" si="4"/>
-        <v>1.5</v>
-      </c>
-      <c r="K12">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="G16">
         <f t="shared" si="2"/>
         <v>1.5</v>
       </c>
-      <c r="L12" cm="1">
-        <f t="array" ref="L12">SUM(VALUE(IF(ISNUMBER(H:H),$A$1*$A$2*$D$2*SIGN(H:H-J12)/(H:H-J12)^2,0)))</f>
-        <v>-8.8824229300050502E-11</v>
-      </c>
+      <c r="I16" s="8">
+        <f>$A$3*$D$4*SIGN($G16-I$4)/($G16-I$4)^2</f>
+        <v>1.9337039384336801E-12</v>
+      </c>
+      <c r="J16" s="8">
+        <f>$A$3*$D$4*SIGN($G16-J$4)/($G16-J$4)^2</f>
+        <v>2.1094083950617284E-12</v>
+      </c>
+      <c r="K16" s="8">
+        <f>$A$3*$D$4*SIGN($G16-K$4)/($G16-K$4)^2</f>
+        <v>2.3101957815035153E-12</v>
+      </c>
+      <c r="L16" s="8">
+        <f>$A$3*$D$4*SIGN($G16-L$4)/($G16-L$4)^2</f>
+        <v>2.5410779298036882E-12</v>
+      </c>
+      <c r="M16" s="8">
+        <f>$A$3*$D$4*SIGN($G16-M$4)/($G16-M$4)^2</f>
+        <v>2.8083839579224193E-12</v>
+      </c>
+      <c r="N16" s="8">
+        <f>$A$3*$D$4*SIGN($G16-N$4)/($G16-N$4)^2</f>
+        <v>3.1201986851716579E-12</v>
+      </c>
+      <c r="O16" s="8">
+        <f>$A$3*$D$4*SIGN($G16-O$4)/($G16-O$4)^2</f>
+        <v>3.4869812244897956E-12</v>
+      </c>
+      <c r="P16" s="8">
+        <f>$A$3*$D$4*SIGN($G16-P$4)/($G16-P$4)^2</f>
+        <v>3.9224536271808994E-12</v>
+      </c>
+      <c r="Q16" s="8">
+        <f>$A$3*$D$4*SIGN($G16-Q$4)/($G16-Q$4)^2</f>
+        <v>4.4449032258064514E-12</v>
+      </c>
+      <c r="R16" s="8">
+        <f>$A$3*$D$4*SIGN($G16-R$4)/($G16-R$4)^2</f>
+        <v>5.0791343638525559E-12</v>
+      </c>
+      <c r="S16" s="8">
+        <f>$A$3*$D$4*SIGN($G16-S$4)/($G16-S$4)^2</f>
+        <v>5.8594677640603565E-12</v>
+      </c>
+      <c r="T16" s="8">
+        <f>$A$3*$D$4*SIGN($G16-T$4)/($G16-T$4)^2</f>
+        <v>6.8344831999999996E-12</v>
+      </c>
+      <c r="U16" s="8">
+        <f>$A$3*$D$4*SIGN($G16-U$4)/($G16-U$4)^2</f>
+        <v>8.0747674858223054E-12</v>
+      </c>
+      <c r="V16" s="8">
+        <f>$A$3*$D$4*SIGN($G16-V$4)/($G16-V$4)^2</f>
+        <v>9.6860589569160981E-12</v>
+      </c>
+      <c r="W16" s="8">
+        <f>$A$3*$D$4*SIGN($G16-W$4)/($G16-W$4)^2</f>
+        <v>1.1832554016620497E-11</v>
+      </c>
+      <c r="X16" s="8">
+        <f>$A$3*$D$4*SIGN($G16-X$4)/($G16-X$4)^2</f>
+        <v>1.4780456747404844E-11</v>
+      </c>
+      <c r="Y16" s="6">
+        <f t="shared" si="1"/>
+        <v>8.8824229300050502E-11</v>
+      </c>
+      <c r="Z16" s="1"/>
+      <c r="AA16" s="1"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="G13">
-        <f t="shared" si="1"/>
-        <v>11</v>
-      </c>
-      <c r="H13">
-        <f t="shared" si="0"/>
-        <v>0.71875</v>
-      </c>
-      <c r="J13">
-        <f t="shared" si="4"/>
-        <v>1.75</v>
-      </c>
-      <c r="K13">
+    <row r="17" spans="7:27" x14ac:dyDescent="0.25">
+      <c r="G17">
         <f t="shared" si="2"/>
         <v>1.75</v>
       </c>
-      <c r="L13" cm="1">
-        <f t="array" ref="L13">SUM(VALUE(IF(ISNUMBER(H:H),$A$1*$A$2*$D$2*SIGN(H:H-J13)/(H:H-J13)^2,0)))</f>
-        <v>-5.0804486853651142E-11</v>
-      </c>
+      <c r="I17" s="8">
+        <f>$A$3*$D$4*SIGN($G17-I$4)/($G17-I$4)^2</f>
+        <v>1.4120833057851238E-12</v>
+      </c>
+      <c r="J17" s="8">
+        <f>$A$3*$D$4*SIGN($G17-J$4)/($G17-J$4)^2</f>
+        <v>1.5206664293342826E-12</v>
+      </c>
+      <c r="K17" s="8">
+        <f>$A$3*$D$4*SIGN($G17-K$4)/($G17-K$4)^2</f>
+        <v>1.6422729719338714E-12</v>
+      </c>
+      <c r="L17" s="8">
+        <f>$A$3*$D$4*SIGN($G17-L$4)/($G17-L$4)^2</f>
+        <v>1.7790720533111202E-12</v>
+      </c>
+      <c r="M17" s="8">
+        <f>$A$3*$D$4*SIGN($G17-M$4)/($G17-M$4)^2</f>
+        <v>1.9337039384336801E-12</v>
+      </c>
+      <c r="N17" s="8">
+        <f>$A$3*$D$4*SIGN($G17-N$4)/($G17-N$4)^2</f>
+        <v>2.1094083950617284E-12</v>
+      </c>
+      <c r="O17" s="8">
+        <f>$A$3*$D$4*SIGN($G17-O$4)/($G17-O$4)^2</f>
+        <v>2.3101957815035153E-12</v>
+      </c>
+      <c r="P17" s="8">
+        <f>$A$3*$D$4*SIGN($G17-P$4)/($G17-P$4)^2</f>
+        <v>2.5410779298036882E-12</v>
+      </c>
+      <c r="Q17" s="8">
+        <f>$A$3*$D$4*SIGN($G17-Q$4)/($G17-Q$4)^2</f>
+        <v>2.8083839579224193E-12</v>
+      </c>
+      <c r="R17" s="8">
+        <f>$A$3*$D$4*SIGN($G17-R$4)/($G17-R$4)^2</f>
+        <v>3.1201986851716579E-12</v>
+      </c>
+      <c r="S17" s="8">
+        <f>$A$3*$D$4*SIGN($G17-S$4)/($G17-S$4)^2</f>
+        <v>3.4869812244897956E-12</v>
+      </c>
+      <c r="T17" s="8">
+        <f>$A$3*$D$4*SIGN($G17-T$4)/($G17-T$4)^2</f>
+        <v>3.9224536271808994E-12</v>
+      </c>
+      <c r="U17" s="8">
+        <f>$A$3*$D$4*SIGN($G17-U$4)/($G17-U$4)^2</f>
+        <v>4.4449032258064514E-12</v>
+      </c>
+      <c r="V17" s="8">
+        <f>$A$3*$D$4*SIGN($G17-V$4)/($G17-V$4)^2</f>
+        <v>5.0791343638525559E-12</v>
+      </c>
+      <c r="W17" s="8">
+        <f>$A$3*$D$4*SIGN($G17-W$4)/($G17-W$4)^2</f>
+        <v>5.8594677640603565E-12</v>
+      </c>
+      <c r="X17" s="8">
+        <f>$A$3*$D$4*SIGN($G17-X$4)/($G17-X$4)^2</f>
+        <v>6.8344831999999996E-12</v>
+      </c>
+      <c r="Y17" s="6">
+        <f t="shared" si="1"/>
+        <v>5.0804486853651142E-11</v>
+      </c>
+      <c r="Z17" s="1"/>
+      <c r="AA17" s="1"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="G14">
-        <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
-      <c r="H14">
-        <f t="shared" si="0"/>
-        <v>0.78125</v>
-      </c>
-      <c r="J14">
-        <f t="shared" si="4"/>
-        <v>2</v>
-      </c>
-      <c r="K14">
+    <row r="18" spans="7:27" x14ac:dyDescent="0.25">
+      <c r="G18">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="L14" cm="1">
-        <f t="array" ref="L14">SUM(VALUE(IF(ISNUMBER(H:H),$A$1*$A$2*$D$2*SIGN(H:H-J14)/(H:H-J14)^2,0)))</f>
-        <v>-3.335251822770423E-11</v>
-      </c>
+      <c r="I18" s="8">
+        <f>$A$3*$D$4*SIGN($G18-I$4)/($G18-I$4)^2</f>
+        <v>1.0762287729906776E-12</v>
+      </c>
+      <c r="J18" s="8">
+        <f>$A$3*$D$4*SIGN($G18-J$4)/($G18-J$4)^2</f>
+        <v>1.1479580757860789E-12</v>
+      </c>
+      <c r="K18" s="8">
+        <f>$A$3*$D$4*SIGN($G18-K$4)/($G18-K$4)^2</f>
+        <v>1.2271048549267451E-12</v>
+      </c>
+      <c r="L18" s="8">
+        <f>$A$3*$D$4*SIGN($G18-L$4)/($G18-L$4)^2</f>
+        <v>1.3147282240689442E-12</v>
+      </c>
+      <c r="M18" s="8">
+        <f>$A$3*$D$4*SIGN($G18-M$4)/($G18-M$4)^2</f>
+        <v>1.4120833057851238E-12</v>
+      </c>
+      <c r="N18" s="8">
+        <f>$A$3*$D$4*SIGN($G18-N$4)/($G18-N$4)^2</f>
+        <v>1.5206664293342826E-12</v>
+      </c>
+      <c r="O18" s="8">
+        <f>$A$3*$D$4*SIGN($G18-O$4)/($G18-O$4)^2</f>
+        <v>1.6422729719338714E-12</v>
+      </c>
+      <c r="P18" s="8">
+        <f>$A$3*$D$4*SIGN($G18-P$4)/($G18-P$4)^2</f>
+        <v>1.7790720533111202E-12</v>
+      </c>
+      <c r="Q18" s="8">
+        <f>$A$3*$D$4*SIGN($G18-Q$4)/($G18-Q$4)^2</f>
+        <v>1.9337039384336801E-12</v>
+      </c>
+      <c r="R18" s="8">
+        <f>$A$3*$D$4*SIGN($G18-R$4)/($G18-R$4)^2</f>
+        <v>2.1094083950617284E-12</v>
+      </c>
+      <c r="S18" s="8">
+        <f>$A$3*$D$4*SIGN($G18-S$4)/($G18-S$4)^2</f>
+        <v>2.3101957815035153E-12</v>
+      </c>
+      <c r="T18" s="8">
+        <f>$A$3*$D$4*SIGN($G18-T$4)/($G18-T$4)^2</f>
+        <v>2.5410779298036882E-12</v>
+      </c>
+      <c r="U18" s="8">
+        <f>$A$3*$D$4*SIGN($G18-U$4)/($G18-U$4)^2</f>
+        <v>2.8083839579224193E-12</v>
+      </c>
+      <c r="V18" s="8">
+        <f>$A$3*$D$4*SIGN($G18-V$4)/($G18-V$4)^2</f>
+        <v>3.1201986851716579E-12</v>
+      </c>
+      <c r="W18" s="8">
+        <f>$A$3*$D$4*SIGN($G18-W$4)/($G18-W$4)^2</f>
+        <v>3.4869812244897956E-12</v>
+      </c>
+      <c r="X18" s="8">
+        <f>$A$3*$D$4*SIGN($G18-X$4)/($G18-X$4)^2</f>
+        <v>3.9224536271808994E-12</v>
+      </c>
+      <c r="Y18" s="6">
+        <f t="shared" si="1"/>
+        <v>3.335251822770423E-11</v>
+      </c>
+      <c r="Z18" s="1"/>
+      <c r="AA18" s="1"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="G15">
-        <f t="shared" si="1"/>
-        <v>13</v>
-      </c>
-      <c r="H15">
-        <f t="shared" si="0"/>
-        <v>0.84375</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="G16">
-        <f t="shared" si="1"/>
-        <v>14</v>
-      </c>
-      <c r="H16">
-        <f t="shared" si="0"/>
-        <v>0.90625</v>
-      </c>
-    </row>
-    <row r="17" spans="7:8" x14ac:dyDescent="0.25">
-      <c r="G17">
-        <f t="shared" si="1"/>
-        <v>15</v>
-      </c>
-      <c r="H17">
-        <f t="shared" si="0"/>
-        <v>0.96875</v>
-      </c>
-    </row>
-    <row r="18" spans="7:8" x14ac:dyDescent="0.25">
-      <c r="G18" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H18" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
+    <row r="19" spans="7:27" x14ac:dyDescent="0.25">
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+      <c r="O19" s="1"/>
+      <c r="P19" s="1"/>
+      <c r="Q19" s="1"/>
+      <c r="R19" s="1"/>
+      <c r="S19" s="1"/>
+      <c r="T19" s="1"/>
+      <c r="U19" s="1"/>
+      <c r="V19" s="1"/>
+      <c r="W19" s="1"/>
+      <c r="X19" s="1"/>
+      <c r="Y19" s="1"/>
+      <c r="Z19" s="1"/>
+      <c r="AA19" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
